--- a/public/crawlability-anbar-september-2026.xlsx
+++ b/public/crawlability-anbar-september-2026.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 22 כתובות (הבולטת: https://anbar.co.il/האם-כדאי-לקחת-משכנתא-הפוכה/, 66 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 21 כתובות (הבולטת: https://anbar.co.il/האם-כדאי-לקחת-משכנתא-הפוכה/, 66 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 3 כתובות (הבולטת: https://anbar.co.il/privacy-policy, 264 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות (הבולטת: https://anbar.co.il/privacy-policy, 264 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של anbar ב-SE Ranking (הסריקה האחרונה: 2024-04-09).</t>
+          <t>להריץ מחדש את ה-Website Audit של anbar ב-SE Ranking (הסריקה האחרונה: 2024-04-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://anbar.co.il/משכנתא-הפוכה-מחשבון/  </t>
+          <t>https://anbar.co.il/משכנתא/</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/משכנתא-הפוכה-מחשבון/</t>
+          <t>https://anbar.co.il/משכנתא-הפוכה/</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/משכנתא-הפוכה-ריבית-2/</t>
+          <t>https://anbar.co.il/הלוואה-כנגד-נכס-קיים-משכנתא-לסגירת-חוב/</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/משכנתא-הפוכה-מחשבון/</t>
+          <t>https://anbar.co.il/משכנתא-הפוכה/</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1828,7 +1828,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/משכנתא/</t>
+          <t>https://anbar.co.il/משכנתא-בלון-כל-מה-שחשוב-לדעת/</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/משכנתא-הפוכה/</t>
+          <t>https://anbar.co.il/עד-איזה-גיל-ניתן-לקחת-משכנתא/#balon</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/הלוואה-כנגד-נכס-קיים-משכנתא-לסגירת-חוב/</t>
+          <t>https://anbar.co.il/מה-ההבדלים-בתנאי-המשכנתא-עבור-דירה-מקב/</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/משכנתא-הפוכה/</t>
+          <t>https://anbar.co.il/עד-איזה-גיל-ניתן-לקחת-משכנתא/#balon</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/משכנתא-בלון-כל-מה-שחשוב-לדעת/</t>
+          <t>https://anbar.co.il/what-to-know-about-reverse-mortgage/</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1892,20 +1892,16 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/עד-איזה-גיל-ניתן-לקחת-משכנתא/#balon</t>
+          <t>https://anbar.co.il/חסרונות-משכנתא-הפוכה-וכיצד-הם-מתגמדים/</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/מה-ההבדלים-בתנאי-המשכנתא-עבור-דירה-מקב/</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
@@ -1913,12 +1909,12 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/עד-איזה-גיל-ניתן-לקחת-משכנתא/#balon</t>
+          <t>https://anbar.co.il/חסרונות-משכנתא-הפוכה-וכיצד-הם-מתגמדים/</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -1930,7 +1926,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/what-to-know-about-reverse-mortgage/</t>
+          <t>https://anbar.co.il/privacy-policy</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -1943,63 +1939,16 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/חסרונות-משכנתא-הפוכה-וכיצד-הם-מתגמדים/</t>
+          <t>https://anbar.co.il/privacy-policy/</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/חסרונות-משכנתא-הפוכה-וכיצד-הם-מתגמדים/</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/privacy-policy</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/privacy-policy/</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2" t="n">
         <v>264</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>https://anbar.co.il/
 https://anbar.co.il/משכנתא-פנסיונית/
@@ -2014,53 +1963,53 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים ללא לוכסן סופי</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>https://anbar.co.il/privacy-policy/</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>בינונית</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>https://anbar.co.il/cookies-policy</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B24" s="2" t="n">
         <v>301</v>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>https://anbar.co.il/cookies-policy/</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>https://anbar.co.il/
 https://anbar.co.il/משכנתא-פנסיונית/
@@ -2075,6 +2024,57 @@
 (ועוד 40)</t>
         </is>
       </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>קישורים פנימיים ללא לוכסן סופי</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>https://anbar.co.il/cookies-policy/</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>בינונית</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://anbar.co.il/משכנתא-הפוכה-מחשבון/  </t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>https://anbar.co.il/משכנתא-הפוכה-מחשבון/</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>https://anbar.co.il/משכנתא-הפוכה-ריבית-2/</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים ללא לוכסן סופי</t>
@@ -2082,17 +2082,17 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
+          <t>הקישור מכיל רווח בסוף הכתובת, והשרת מפנה לכתובת ללא הרווח. לתקן את הקישור בעמודי המקור.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/cookies-policy/</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+          <t>https://anbar.co.il/משכנתא-הפוכה-מחשבון/</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>

--- a/public/crawlability-anbar-september-2026.xlsx
+++ b/public/crawlability-anbar-september-2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 21 כתובות (הבולטת: https://anbar.co.il/האם-כדאי-לקחת-משכנתא-הפוכה/, 66 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 20 כתובות (הבולטת: https://anbar.co.il/האם-כדאי-לקחת-משכנתא-הפוכה/, 66 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -532,14 +532,14 @@
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 4 כתובות (הבולטת: https://anbar.co.il/privacy-policy, 264 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 3 כתובות (הבולטת: https://anbar.co.il/privacy-policy, 264 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -553,6 +553,21 @@
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>קישורים עם רווח בסוף הכתובת: כתובת אחת (הבולטת: https://anbar.co.il/משכנתא-הפוכה-מחשבון/ [רווח בסוף], קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>להריץ מחדש את ה-Website Audit של anbar ב-SE Ranking (הסריקה האחרונה: 2024-04-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
@@ -705,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1879,7 +1894,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/what-to-know-about-reverse-mortgage/</t>
+          <t>https://anbar.co.il/privacy-policy</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1892,63 +1907,16 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/חסרונות-משכנתא-הפוכה-וכיצד-הם-מתגמדים/</t>
+          <t>https://anbar.co.il/privacy-policy/</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/חסרונות-משכנתא-הפוכה-וכיצד-הם-מתגמדים/</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/privacy-policy</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/privacy-policy/</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="2" t="n">
         <v>264</v>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>https://anbar.co.il/
 https://anbar.co.il/משכנתא-פנסיונית/
@@ -1963,53 +1931,53 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים ללא לוכסן סופי</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>https://anbar.co.il/privacy-policy/</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>בינונית</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>https://anbar.co.il/cookies-policy</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B23" s="2" t="n">
         <v>301</v>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>301 -&gt; 200</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>https://anbar.co.il/cookies-policy/</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F23" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>https://anbar.co.il/
 https://anbar.co.il/משכנתא-פנסיונית/
@@ -2024,6 +1992,57 @@
 (ועוד 40)</t>
         </is>
       </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>קישורים פנימיים ללא לוכסן סופי</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>https://anbar.co.il/cookies-policy/</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>בינונית</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>https://anbar.co.il/loan-against-property</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>https://anbar.co.il/loan-against-property/</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>https://anbar.co.il/משכנתא-לדירה-מפוצלת-המדריך-המלא/</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>קישורים פנימיים ללא לוכסן סופי</t>
@@ -2036,112 +2055,10 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>https://anbar.co.il/cookies-policy/</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://anbar.co.il/משכנתא-הפוכה-מחשבון/  </t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/משכנתא-הפוכה-מחשבון/</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/משכנתא-הפוכה-ריבית-2/</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים ללא לוכסן סופי</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>הקישור מכיל רווח בסוף הכתובת, והשרת מפנה לכתובת ללא הרווח. לתקן את הקישור בעמודי המקור.</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/משכנתא-הפוכה-מחשבון/</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/loan-against-property</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
           <t>https://anbar.co.il/loan-against-property/</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/משכנתא-לדירה-מפוצלת-המדריך-המלא/</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים ללא לוכסן סופי</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>https://anbar.co.il/loan-against-property/</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -2269,7 +2186,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>קישורי Cloudflare (ללא טיפול)</t>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">

--- a/public/crawlability-anbar-september-2026.xlsx
+++ b/public/crawlability-anbar-september-2026.xlsx
@@ -1308,7 +1308,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">

--- a/public/crawlability-anbar-september-2026.xlsx
+++ b/public/crawlability-anbar-september-2026.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>שרשראות הפניות: כתובת אחת (הבולטת: https://anbar.co.il/reverse-mortgage-2021/, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>שרשראות הפניות: כתובת אחת; הבולטת https://anbar.co.il/reverse-mortgage-2021/ (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 20 כתובות (הבולטת: https://anbar.co.il/האם-כדאי-לקחת-משכנתא-הפוכה/, 66 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 20 כתובות; הבולטת https://anbar.co.il/האם-כדאי-לקחת-משכנתא-הפוכה/ (66 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 3 כתובות (הבולטת: https://anbar.co.il/privacy-policy, 264 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 3 כתובות; הבולטת https://anbar.co.il/privacy-policy (264 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>קישורים עם רווח בסוף הכתובת: כתובת אחת (הבולטת: https://anbar.co.il/משכנתא-הפוכה-מחשבון/ [רווח בסוף], קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים עם רווח בסוף הכתובת: כתובת אחת; הבולטת https://anbar.co.il/משכנתא-הפוכה-מחשבון/ [רווח בסוף] (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של anbar ב-SE Ranking (הסריקה האחרונה: 2024-04-09); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של anbar ב-SE Ranking; הסריקה האחרונה: 2024-04-09.</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2151,25 +2151,72 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>https://anbar.co.il/what-to-know-about-reverse-mortgage/</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>https://anbar.co.il/חסרונות-משכנתא-הפוכה-וכיצד-הם-מתגמדים/</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>https://anbar.co.il/חסרונות-משכנתא-הפוכה-וכיצד-הם-מתגמדים/</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>https://anbar.co.il/cdn-cgi/l/email-protection</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B3" s="2" t="n">
         <v>404</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>https://anbar.co.il/
 https://anbar.co.il/משכנתא-פנסיונית/
@@ -2184,18 +2231,18 @@
 (ועוד 40)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>קישור הגנת דוא"ל של Cloudflare (cdn-cgi). גוגל מתעלם מכתובות cdn-cgi; לא נדרש טיפול. ניתן לבטל את Email Address Obfuscation ב-Cloudflare כדי שהסורקים לא ידווחו על כך.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>

--- a/public/crawlability-anbar-september-2026.xlsx
+++ b/public/crawlability-anbar-september-2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר 28 כתובות שמפנות (301/302) ולהשאיר את כתובות היעד בלבד.</t>
+          <t>להסיר ממפת האתר 28 כתובות שמפנות (301/302) (באתר WordPress/Yoast: להעביר את העמודים המפנים לטיוטה או להחריגם מה-sitemap; המפה נוצרת אוטומטית).</t>
         </is>
       </c>
     </row>
@@ -555,21 +555,6 @@
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>קישורים עם רווח בסוף הכתובת: כתובת אחת; הבולטת https://anbar.co.il/משכנתא-הפוכה-מחשבון/ [רווח בסוף] (קישור נכנס אחד).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של anbar ב-SE Ranking; הסריקה האחרונה: 2024-04-09.</t>
         </is>
       </c>
     </row>
